--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.52886303556375</v>
+        <v>10.48594024327911</v>
       </c>
       <c r="D2" t="n">
-        <v>64.18508709161244</v>
+        <v>10.43007665238702</v>
       </c>
       <c r="E2" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F2" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.34059719928083</v>
+        <v>8.667847044883136</v>
       </c>
       <c r="D3" t="n">
-        <v>52.95151687794868</v>
+        <v>8.604621492666661</v>
       </c>
       <c r="E3" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F3" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.6351634496867</v>
+        <v>3.678214060574089</v>
       </c>
       <c r="D4" t="n">
-        <v>22.91796693593929</v>
+        <v>3.724169627090135</v>
       </c>
       <c r="E4" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F4" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.12314921174119</v>
+        <v>8.145011746907944</v>
       </c>
       <c r="D5" t="n">
-        <v>49.85889076099652</v>
+        <v>8.102069748661936</v>
       </c>
       <c r="E5" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F5" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.85117923142959</v>
+        <v>5.175816625107308</v>
       </c>
       <c r="D6" t="n">
-        <v>31.80510352239916</v>
+        <v>5.168329322389864</v>
       </c>
       <c r="E6" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F6" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.71718267156454</v>
+        <v>2.879042184129238</v>
       </c>
       <c r="D7" t="n">
-        <v>17.33461530242215</v>
+        <v>2.8168749866436</v>
       </c>
       <c r="E7" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F7" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.40778612978929</v>
+        <v>10.62876524609076</v>
       </c>
       <c r="D8" t="n">
-        <v>65.69662222657696</v>
+        <v>10.67570111181876</v>
       </c>
       <c r="E8" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F8" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.64974541511324</v>
+        <v>8.393083629955903</v>
       </c>
       <c r="D9" t="n">
-        <v>52.01258625958278</v>
+        <v>8.452045267182202</v>
       </c>
       <c r="E9" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F9" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>21.02485514617604</v>
+        <v>3.416538961253607</v>
       </c>
       <c r="D10" t="n">
-        <v>19.74467283831536</v>
+        <v>3.208509336226246</v>
       </c>
       <c r="E10" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F10" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.5677283266397</v>
+        <v>3.667255853078951</v>
       </c>
       <c r="D11" t="n">
-        <v>5.482622283666752</v>
+        <v>0.8909261210958473</v>
       </c>
       <c r="E11" t="n">
-        <v>17.86538650614679</v>
+        <v>2.903125307248854</v>
       </c>
       <c r="F11" t="n">
-        <v>20.23966135321905</v>
+        <v>3.288944969898095</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
